--- a/nr-create-FrPractitionerRole/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-create-FrPractitionerRole/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$125</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4572" uniqueCount="565">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:44:52+00:00</t>
+    <t>2024-06-11T16:34:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1431,6 +1434,10 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:code}
+</t>
+  </si>
+  <si>
     <t>CER?</t>
   </si>
   <si>
@@ -1496,49 +1503,258 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
+    <t>Specific qualification the practitioner has to provide a service.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-2.7-0360</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
+    <t>./Qualifications.Value</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid.</t>
+  </si>
+  <si>
+    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>.playingEntity.playingRole[classCode=QUAL].effectiveTime</t>
+  </si>
+  <si>
+    <t>./Qualifications.StartDate and ./Qualifications.EndDate</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.issuer</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>.playingEntity.playingRole[classCode=QUAL].scoper</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>Diplôme et type de diplôme, par exemple : DE, DES, CES, etc. (typeDiplome)</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J105-EnsembleDiplome-RASS/FHIR/JDV-J105-EnsembleDiplome-RASS</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>./Qualifications.Value</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period</t>
-  </si>
-  <si>
-    <t>Period during which the qualification is valid</t>
-  </si>
-  <si>
-    <t>Period during which the qualification is valid.</t>
-  </si>
-  <si>
-    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
-  </si>
-  <si>
-    <t>DR</t>
-  </si>
-  <si>
-    <t>.playingEntity.playingRole[classCode=QUAL].effectiveTime</t>
-  </si>
-  <si>
-    <t>./Qualifications.StartDate and ./Qualifications.EndDate</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.issuer</t>
-  </si>
-  <si>
-    <t>Organization that regulates and issues the qualification</t>
-  </si>
-  <si>
-    <t>Organization that regulates and issues the qualification.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>.playingEntity.playingRole[classCode=QUAL].scoper</t>
+    <t>Practitioner.qualification:degree.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
+  </si>
+  <si>
+    <t>categorieProfession</t>
+  </si>
+  <si>
+    <t>Catégorie professionnelle indiquant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:profession</t>
+  </si>
+  <si>
+    <t>profession</t>
+  </si>
+  <si>
+    <t>Profession exercée : de santé (professionSante) TRE G15, du social (professionSocial) TRE R94, à usage de titre professionnel (usagerTitre) TRE R95, ou autre profession (autreProfession) TRE R291</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J106-EnsembleProfession-RASS/FHIR/JDV-J106-EnsembleProfession-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.issuer</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire</t>
+  </si>
+  <si>
+    <t>savoirFaire</t>
+  </si>
+  <si>
+    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>Le type de savoir-faire (qualifications/autres attributions).
+typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J91-TypeSavoirFaire-RASS/FHIR/JDV-J91-TypeSavoirFaire-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:savoirFaire</t>
+  </si>
+  <si>
+    <t>Compétence acquise par le professionnel (competence) R39 ou Compétence exclusive exercée par le professionnel à titre exclusif (competenceExclusive) R40 ou Diplôme d'études spécialisées complémentaires (DESC)DESCnonQualifian R42 ou Capacité (savoir-faire)de médecine (capaciteSavoirFaire) R43 ou Qualification de praticien adjoint contractuel (qualificationPAC) R44 ou Fonction qualifiée (Synonyme: fonctionQualifiee) R45 ou Droit d'exercice complémentaire (Synonyme: droitExerciceComplementaire) R97 ou Orientation particulière (Synonyme: orientationParticuliere) G13 ou Activité ponctuelle du professionnel de type expertise (attributionParticuliere) G13.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J107-EnsembleSavoirFaire-RASS/FHIR/JDV-J107-EnsembleSavoirFaire-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.issuer</t>
   </si>
   <si>
     <t>Practitioner.communication</t>
@@ -1691,6 +1907,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1872,12 +2103,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN83"/>
+  <dimension ref="A1:AN125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.38671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.38671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.15625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1900,7 +2131,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.73828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="107.80859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2038,7 +2269,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -2150,7 +2381,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>88</v>
       </c>
@@ -2264,7 +2495,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>96</v>
       </c>
@@ -2376,7 +2607,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>104</v>
       </c>
@@ -2488,7 +2719,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>110</v>
       </c>
@@ -2602,7 +2833,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>121</v>
       </c>
@@ -2716,7 +2947,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -2830,7 +3061,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>132</v>
       </c>
@@ -2944,7 +3175,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>138</v>
       </c>
@@ -3058,7 +3289,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3174,7 +3405,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>148</v>
       </c>
@@ -3288,7 +3519,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>159</v>
       </c>
@@ -3402,7 +3633,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>167</v>
       </c>
@@ -3516,7 +3747,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -3630,7 +3861,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>181</v>
       </c>
@@ -3744,7 +3975,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
@@ -3858,7 +4089,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>196</v>
       </c>
@@ -3972,7 +4203,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>199</v>
       </c>
@@ -4086,7 +4317,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>204</v>
       </c>
@@ -4202,7 +4433,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>209</v>
       </c>
@@ -4316,7 +4547,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>220</v>
       </c>
@@ -4428,7 +4659,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>221</v>
       </c>
@@ -4542,7 +4773,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>222</v>
       </c>
@@ -4658,7 +4889,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>232</v>
       </c>
@@ -4772,7 +5003,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>241</v>
       </c>
@@ -4884,7 +5115,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>242</v>
       </c>
@@ -4998,7 +5229,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>243</v>
       </c>
@@ -5114,7 +5345,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>251</v>
       </c>
@@ -5226,7 +5457,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>252</v>
       </c>
@@ -5340,7 +5571,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>253</v>
       </c>
@@ -5456,7 +5687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>262</v>
       </c>
@@ -5570,7 +5801,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>269</v>
       </c>
@@ -5686,7 +5917,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>277</v>
       </c>
@@ -5802,7 +6033,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>284</v>
       </c>
@@ -5918,7 +6149,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>293</v>
       </c>
@@ -6034,7 +6265,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>301</v>
       </c>
@@ -6150,7 +6381,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>311</v>
       </c>
@@ -6264,7 +6495,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>320</v>
       </c>
@@ -6378,7 +6609,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>330</v>
       </c>
@@ -6492,7 +6723,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>340</v>
       </c>
@@ -6608,7 +6839,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>343</v>
       </c>
@@ -6720,7 +6951,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>344</v>
       </c>
@@ -6834,7 +7065,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>345</v>
       </c>
@@ -6950,7 +7181,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>346</v>
       </c>
@@ -7066,7 +7297,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>351</v>
       </c>
@@ -7182,7 +7413,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>354</v>
       </c>
@@ -7296,7 +7527,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>356</v>
       </c>
@@ -7410,7 +7641,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>357</v>
       </c>
@@ -7524,7 +7755,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>358</v>
       </c>
@@ -7640,7 +7871,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>361</v>
       </c>
@@ -7752,7 +7983,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>362</v>
       </c>
@@ -7866,7 +8097,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>363</v>
       </c>
@@ -7982,7 +8213,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>364</v>
       </c>
@@ -8098,7 +8329,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>366</v>
       </c>
@@ -8214,7 +8445,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>368</v>
       </c>
@@ -8328,7 +8559,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>369</v>
       </c>
@@ -8442,7 +8673,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>370</v>
       </c>
@@ -8556,7 +8787,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>371</v>
       </c>
@@ -8672,7 +8903,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>374</v>
       </c>
@@ -8784,7 +9015,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>375</v>
       </c>
@@ -8898,7 +9129,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>376</v>
       </c>
@@ -9014,7 +9245,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>377</v>
       </c>
@@ -9130,7 +9361,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>379</v>
       </c>
@@ -9246,7 +9477,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>381</v>
       </c>
@@ -9360,7 +9591,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>382</v>
       </c>
@@ -9474,7 +9705,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>383</v>
       </c>
@@ -9588,7 +9819,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>384</v>
       </c>
@@ -9706,7 +9937,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>392</v>
       </c>
@@ -9822,7 +10053,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>401</v>
       </c>
@@ -9938,7 +10169,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>411</v>
       </c>
@@ -10054,7 +10285,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>420</v>
       </c>
@@ -10170,7 +10401,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>429</v>
       </c>
@@ -10284,7 +10515,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>437</v>
       </c>
@@ -10400,7 +10631,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>447</v>
       </c>
@@ -10419,7 +10650,7 @@
         <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>78</v>
@@ -10473,16 +10704,14 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>447</v>
@@ -10500,24 +10729,24 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10624,12 +10853,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10738,16 +10967,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10769,10 +10998,10 @@
         <v>112</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>115</v>
@@ -10827,7 +11056,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -10854,12 +11083,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10885,14 +11114,14 @@
         <v>210</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -10941,7 +11170,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -10956,24 +11185,24 @@
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10999,13 +11228,13 @@
         <v>233</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11031,11 +11260,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>473</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11053,7 +11284,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>89</v>
@@ -11068,24 +11299,24 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11111,16 +11342,16 @@
         <v>321</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>324</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -11169,7 +11400,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11184,24 +11415,24 @@
         <v>326</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11227,13 +11458,13 @@
         <v>331</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11283,7 +11514,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11301,7 +11532,7 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11310,14 +11541,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C83" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="D83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11329,7 +11562,7 @@
         <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>78</v>
@@ -11338,20 +11571,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>233</v>
+        <v>448</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11375,13 +11604,13 @@
         <v>78</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>78</v>
@@ -11399,7 +11628,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>487</v>
+        <v>447</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11414,19 +11643,4845 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="AL83" t="s" s="2">
+      <c r="B84" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="AM83" t="s" s="2">
+      <c r="B85" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AN83" t="s" s="2">
+      <c r="B86" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AC91" s="2"/>
+      <c r="AD91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y92" s="2"/>
+      <c r="Z92" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y93" s="2"/>
+      <c r="Z93" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="D97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
+      <c r="P103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AC105" s="2"/>
+      <c r="AD105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="D106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y106" s="2"/>
+      <c r="Z106" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="D107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O107" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y107" s="2"/>
+      <c r="Z107" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="D111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O114" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AC119" s="2"/>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="D120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y120" s="2"/>
+      <c r="Z120" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="D121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="P121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="Y121" s="2"/>
+      <c r="Z121" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="P122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="125" hidden="true">
+      <c r="A125" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E125" s="2"/>
+      <c r="F125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q125" s="2"/>
+      <c r="R125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL125" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN125" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AN125">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI124">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/nr-create-FrPractitionerRole/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-create-FrPractitionerRole/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T16:34:47+00:00</t>
+    <t>2024-06-11T16:42:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-create-FrPractitionerRole/ig/StructureDefinition-fr-core-practitioner.xlsx
+++ b/nr-create-FrPractitionerRole/ig/StructureDefinition-fr-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T16:42:33+00:00</t>
+    <t>2024-06-11T16:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
